--- a/by World_bank_classification.xlsx
+++ b/by World_bank_classification.xlsx
@@ -51,27 +51,7 @@
     <t xml:space="preserve">False discovery rate correction for multiple testing</t>
   </si>
   <si>
-    <t xml:space="preserve">high_income
-N = 469
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,195 (1,690, 4,000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7 (1.9, 4.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64 (0.43, 0.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,276 (1,363, 7,822)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5 (2.1, 6.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower_middle_income
+    <t xml:space="preserve">.lower_middle_income
 N = 14
 </t>
   </si>
@@ -91,7 +71,7 @@
     <t xml:space="preserve">1.2 (0.7, 1.5)</t>
   </si>
   <si>
-    <t xml:space="preserve">upper_middle_income
+    <t xml:space="preserve">.upper_middle_income
 N = 49
 </t>
   </si>
@@ -109,6 +89,26 @@
   </si>
   <si>
     <t xml:space="preserve">0.8 (0.3, 1.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high_income
+N = 471
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,190 (1,690, 4,000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7 (1.9, 4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64 (0.43, 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,276 (1,363, 7,822)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5 (2.0, 6.7)</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
@@ -625,13 +625,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>32</v>
@@ -665,13 +665,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>32</v>
@@ -705,13 +705,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>32</v>
@@ -745,13 +745,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>32</v>
@@ -785,13 +785,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
